--- a/SGC-CKN/Excel/77f20ee4-7e98-4da3-9935-089c1130104a_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_D1-171_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/77f20ee4-7e98-4da3-9935-089c1130104a_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_D1-171_D800_19-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>D1-171</t>
+    <t>P11-171</t>
   </si>
   <si>
     <t>Biên bản số</t>

--- a/SGC-CKN/Excel/77f20ee4-7e98-4da3-9935-089c1130104a_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_D1-171_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/77f20ee4-7e98-4da3-9935-089c1130104a_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_D1-171_D800_19-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P11-171</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>M3-3.1.1.2.6</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Đất thổ nhường</t>
+    <t>Đất san lấp / Cát san lấp</t>
   </si>
   <si>
     <t xml:space="preserve">21:10
@@ -106,9 +106,6 @@
 18/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -122,7 +119,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">23:00
@@ -162,7 +159,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt. Chạm sỏi</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">04:50
@@ -175,7 +172,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">06:48
@@ -1180,24 +1177,24 @@
         <v>0.69</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="9">
         <v>-0.9</v>
@@ -1215,24 +1212,24 @@
         <v>3.87</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-3.8</v>
@@ -1250,24 +1247,24 @@
         <v>4.53</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>39</v>
       </c>
       <c r="F14" s="16">
         <v>-7.2</v>
@@ -1285,24 +1282,24 @@
         <v>2.87</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>41</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="19">
         <v>-15.8</v>
@@ -1320,24 +1317,24 @@
         <v>5.2</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="25" t="s">
         <v>44</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>45</v>
       </c>
       <c r="F16" s="23">
         <v>-21</v>
@@ -1355,24 +1352,24 @@
         <v>4.8</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="28" t="s">
         <v>47</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>48</v>
       </c>
       <c r="F17" s="26">
         <v>-25.8</v>
@@ -1390,24 +1387,24 @@
         <v>12.43</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="31" t="s">
         <v>51</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>52</v>
       </c>
       <c r="F18" s="29">
         <v>-36.16</v>
@@ -1425,12 +1422,12 @@
         <v>4.16</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -1536,31 +1533,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1600,7 +1597,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1629,7 +1626,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1658,7 +1655,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1687,7 +1684,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1716,7 +1713,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="23">
         <v>1</v>
@@ -1745,7 +1742,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="26">
         <v>1</v>
@@ -1774,7 +1771,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="29">
         <v>1</v>
@@ -1797,13 +1794,13 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D10" s="34">
         <v>8</v>

--- a/SGC-CKN/Excel/77f20ee4-7e98-4da3-9935-089c1130104a_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_D1-171_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/77f20ee4-7e98-4da3-9935-089c1130104a_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_D1-171_D800_19-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="62">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGCT-KCN0003</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -106,10 +106,13 @@
 18/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">22:15
@@ -129,9 +132,6 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">02:00
 19/03/2026</t>
   </si>
@@ -149,7 +149,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">04:00
@@ -157,9 +157,6 @@
   </si>
   <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">04:50
@@ -216,7 +213,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -288,11 +285,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF164E63"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -305,7 +297,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -375,11 +367,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5F3FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -475,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -561,22 +548,13 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1177,24 +1155,24 @@
         <v>0.69</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-0.9</v>
@@ -1212,24 +1190,24 @@
         <v>3.87</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-3.8</v>
@@ -1247,21 +1225,21 @@
         <v>4.53</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="18" t="s">
         <v>38</v>
@@ -1282,7 +1260,7 @@
         <v>2.87</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1317,7 +1295,7 @@
         <v>5.2</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1352,93 +1330,93 @@
         <v>4.8</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="26">
+      <c r="F17" s="23">
         <v>-25.8</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="23">
         <v>-36.16</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="23">
         <v>0.83</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="23">
         <v>10.36</v>
       </c>
       <c r="J17" s="22">
         <v>12.43</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K17" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="26" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="B18" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="30" t="s">
+      <c r="D18" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="29">
+      <c r="F18" s="26">
         <v>-36.16</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="26">
         <v>-44.35</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="26">
         <v>1.97</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="26">
         <v>8.19</v>
       </c>
       <c r="J18" s="12">
         <v>4.16</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="29" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1520,7 +1498,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1533,31 +1511,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1597,7 +1575,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1626,7 +1604,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1655,7 +1633,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1716,22 +1694,22 @@
         <v>43</v>
       </c>
       <c r="D7" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="23">
         <v>-21</v>
       </c>
       <c r="F7" s="23">
-        <v>-25.8</v>
+        <v>-36.16</v>
       </c>
       <c r="G7" s="23">
-        <v>1</v>
+        <v>1.83</v>
       </c>
       <c r="H7" s="23">
-        <v>4.8</v>
-      </c>
-      <c r="I7" s="12">
-        <v>4.8</v>
+        <v>15.16</v>
+      </c>
+      <c r="I7" s="22">
+        <v>8.27</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1742,82 +1720,53 @@
         <v>11</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D8" s="26">
         <v>1</v>
       </c>
       <c r="E8" s="26">
-        <v>-25.8</v>
+        <v>-36.16</v>
       </c>
       <c r="F8" s="26">
-        <v>-36.16</v>
+        <v>-44.35</v>
       </c>
       <c r="G8" s="26">
-        <v>0.83</v>
+        <v>1.97</v>
       </c>
       <c r="H8" s="26">
-        <v>10.36</v>
-      </c>
-      <c r="I8" s="22">
-        <v>12.43</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+        <v>8.19</v>
+      </c>
+      <c r="I8" s="12">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="31">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="29">
-        <v>1</v>
-      </c>
-      <c r="E9" s="29">
-        <v>-36.16</v>
-      </c>
-      <c r="F9" s="29">
+      <c r="E9" s="31">
+        <v>-0.67</v>
+      </c>
+      <c r="F9" s="31">
         <v>-44.35</v>
       </c>
-      <c r="G9" s="29">
-        <v>1.97</v>
-      </c>
-      <c r="H9" s="29">
-        <v>8.19</v>
-      </c>
-      <c r="I9" s="12">
-        <v>4.16</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="34">
-        <v>8</v>
-      </c>
-      <c r="E10" s="34">
-        <v>-0.67</v>
-      </c>
-      <c r="F10" s="34">
-        <v>-44.35</v>
-      </c>
-      <c r="G10" s="34">
+      <c r="G9" s="31">
         <v>9.63</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H9" s="31">
         <v>43.68</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I9" s="31">
         <v>4.53</v>
       </c>
     </row>

--- a/SGC-CKN/Excel/77f20ee4-7e98-4da3-9935-089c1130104a_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_D1-171_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/77f20ee4-7e98-4da3-9935-089c1130104a_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_D1-171_D800_19-03-2026.xlsx
@@ -23,7 +23,7 @@
     <t>Hạng mục</t>
   </si>
   <si>
-    <t>Thi công cọc khoan nhồi đại trà_lô đất ký hiệu CT-02</t>
+    <t>Thi công cọc khoan nhồi, tường vây cho các hạng mục_Lô CT-02</t>
   </si>
   <si>
     <t>Tên bộ phận</t>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P11-171</t>
+    <t>P1-171</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
